--- a/spreadsheets/visual_art.xlsx
+++ b/spreadsheets/visual_art.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hamish.patten/Documents/Coding/mywebsite/spreadsheets/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0BF4FF9-8946-A14D-903E-044549F6F762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -22,123 +27,104 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subtitle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Image</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Existentialism</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lausanne, June 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logical intelligence; maths, statistics, physics, programming and other disciplines; have been promoted as being the superior intelligence globally for hundreds of years. This type of intelligence is the easiest for Agentic AI tools to replace. For people who dedicated their lives to trying to excel in such domains, the toppling of logical intelligence results in great uncertainty in ones life decisions and value system, provoking nihilist and existential ideation. This painting illustrates the start of such realisation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Images/Visual_Art/self_portrait.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drogue-toi, Folklor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lausanne, May 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moralist perspectives are culturally subjective and absurd; when objective meaning feels impossibly out-of-reach, there is a fine line between freedom and emptiness. Drug usage can play a role in such environments. Folkor, Lausanne, is a club known for drug consumption. Sitting right underneath one of the most ornate and grandiose buildings of the city, the public library, the stark contrast with the hidden, simple and rugged appearance of Folklor is unmistakable.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Images/Visual_Art/folklor.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meduse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lausanne, April 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jellyfish, or meduse in french, have different interpretations depending on the viewer. Seeing one for the first time, without knowledge of the potential to afflict pain, one might fall in love with such beauty. On the contrary, after gaining such knowledge, fear and aversion takes place. To what extent do we forget the beauty of our first impression once fear settles in? What would it mean to think of oneself as the meduse?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Images/Visual_Art/big_jelly.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meduse in Watercolour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">London, January 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The negative space that one can create with watercolour can give a completely different dimension to painting. In a study of self-loathing, I use the jellyfish to explore human perception and fragility, hoping to move towards self-acceptance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Images/Visual_Art/water_jelly.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brighton Old Pier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lausanne, November 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Brighton Old Pier burned down in 2003, with its metallic structure remaining and directly observable from the shore. This painting depicts how depression can be unobservable and incomprehensible, even by those closest to you. My parents are the two characters in the painting, enjoying looking over a family memory: when we swam the channel as a family relay in 2013, our entire family did several training swims around the old and new piers in Brighton. This watercolour piece represents what it feels like to have your entire life burnt down and to have onlookers that have no idea what you are going through, even those closest to you</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Images/Visual_Art/brighton.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Homesickness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lausanne, August 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The grass is always greener on the other side, but what happens if you grew up and culturally associate far more with that 'other side'? Having spent over seven years in Lausanne, Switzerland, at the time of this painting, I explore painting parts of England that I have never even visited: Gold Hill, Shaftesbury.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Images/Visual_Art/goldhill.jpg</t>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Subtitle</t>
+  </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>File</t>
+  </si>
+  <si>
+    <t>Image</t>
+  </si>
+  <si>
+    <t>AI Existentialism</t>
+  </si>
+  <si>
+    <t>Lausanne, June 2026</t>
+  </si>
+  <si>
+    <t>Logical intelligence; maths, statistics, physics, programming and other disciplines; have been promoted as being the superior intelligence globally for hundreds of years. This type of intelligence is the easiest for Agentic AI tools to replace. For people who dedicated their lives to trying to excel in such domains, the toppling of logical intelligence results in great uncertainty in ones life decisions and value system, provoking nihilist and existential ideation. This painting illustrates the start of such realisation.</t>
+  </si>
+  <si>
+    <t>Images/Visual_Art/self_portrait.jpg</t>
+  </si>
+  <si>
+    <t>Drogue-toi, Folklor</t>
+  </si>
+  <si>
+    <t>Lausanne, May 2026</t>
+  </si>
+  <si>
+    <t>Images/Visual_Art/folklor.jpg</t>
+  </si>
+  <si>
+    <t>Meduse</t>
+  </si>
+  <si>
+    <t>Lausanne, April 2026</t>
+  </si>
+  <si>
+    <t>Jellyfish, or meduse in french, have different interpretations depending on the viewer. Seeing one for the first time, without knowledge of the potential to afflict pain, one might fall in love with such beauty. On the contrary, after gaining such knowledge, fear and aversion takes place. To what extent do we forget the beauty of our first impression once fear settles in? What would it mean to think of oneself as the meduse?</t>
+  </si>
+  <si>
+    <t>Images/Visual_Art/big_jelly.jpg</t>
+  </si>
+  <si>
+    <t>Meduse in Watercolour</t>
+  </si>
+  <si>
+    <t>London, January 2026</t>
+  </si>
+  <si>
+    <t>The negative space that one can create with watercolour can give a completely different dimension to painting. In a study of self-loathing, I use the jellyfish to explore human perception and fragility, hoping to move towards self-acceptance</t>
+  </si>
+  <si>
+    <t>Images/Visual_Art/water_jelly.jpg</t>
+  </si>
+  <si>
+    <t>Brighton Old Pier</t>
+  </si>
+  <si>
+    <t>Lausanne, November 2025</t>
+  </si>
+  <si>
+    <t>The Brighton Old Pier burned down in 2003, with its metallic structure remaining and directly observable from the shore. This painting depicts how depression can be unobservable and incomprehensible, even by those closest to you. My parents are the two characters in the painting, enjoying looking over a family memory: when we swam the channel as a family relay in 2013, our entire family did several training swims around the old and new piers in Brighton. This watercolour piece represents what it feels like to have your entire life burnt down and to have onlookers that have no idea what you are going through, even those closest to you</t>
+  </si>
+  <si>
+    <t>Images/Visual_Art/brighton.jpg</t>
+  </si>
+  <si>
+    <t>Homesickness</t>
+  </si>
+  <si>
+    <t>Lausanne, August 2025</t>
+  </si>
+  <si>
+    <t>The grass is always greener on the other side, but what happens if you grew up and culturally associate far more with that 'other side'? Having spent over seven years in Lausanne, Switzerland, at the time of this painting, I explore painting parts of England that I have never even visited: Gold Hill, Shaftesbury.</t>
+  </si>
+  <si>
+    <t>Images/Visual_Art/goldhill.jpg</t>
+  </si>
+  <si>
+    <t>If moralist perspectives are culturally subjective and absurd and objective meaning feels impossibly out-of-reach, there is a fine line between freedom and emptiness. Drug usage can play a role in such environments. Folkor, Lausanne, is a club known for drug consumption. Sitting right underneath one of the most ornate and grandiose buildings of the city, the public library, the stark contrast with the hidden, simple and rugged appearance of Folklor is unmistakable.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="mmm\-yy"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -150,7 +136,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -158,109 +144,78 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0e2841"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e8e8e8"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="e97132"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196b24"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0f9ed5"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="a02b93"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4ea72e"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607d"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -292,7 +247,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -316,7 +271,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -376,133 +331,127 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="10.55078125" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8.68"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="3" t="s">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="E5" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="3" t="s">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="E6" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="3" t="s">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="E7" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>28</v>
-      </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>